--- a/results/full_enron_split_summary/enron_PartialAbstention_summary.xlsx
+++ b/results/full_enron_split_summary/enron_PartialAbstention_summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC9"/>
+  <dimension ref="A1:BU9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,100 +476,320 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>afrd_pa__0.0</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>afrd_pa__0.1</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>afrd_pa__0.2</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>afrd_pa__0.3</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>arec__0.0</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>arec__0.1</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>arec__0.2</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>arec__0.3</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>example_precision_pa__0.0</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>example_precision_pa__0.1</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>example_precision_pa__0.2</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>example_precision_pa__0.3</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>example_recall_pa__0.0</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>example_recall_pa__0.1</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>example_recall_pa__0.2</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>example_recall_pa__0.3</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>f1_pa__0.0</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>f1_pa__0.1</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>f1_pa__0.2</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>f1_pa__0.3</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>hamming_accuracy_pa__0.0</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>hamming_accuracy_pa__0.1</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>hamming_accuracy_pa__0.2</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>hamming_accuracy_pa__0.3</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>jaccard_pa__0.0</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>jaccard_pa__0.1</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>jaccard_pa__0.2</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>jaccard_pa__0.3</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>macro_f1_pa__0.0</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>macro_f1_pa__0.1</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>macro_f1_pa__0.2</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>macro_f1_pa__0.3</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>macro_precision_pa__0.0</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>macro_precision_pa__0.1</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>macro_precision_pa__0.2</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>macro_precision_pa__0.3</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>macro_recall_pa__0.0</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>macro_recall_pa__0.1</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>macro_recall_pa__0.2</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>macro_recall_pa__0.3</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>mfrd_pa__0.0</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>mfrd_pa__0.1</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>mfrd_pa__0.2</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>mfrd_pa__0.3</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>micro_f1_pa__0.0</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>micro_f1_pa__0.1</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>micro_f1_pa__0.2</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>micro_f1_pa__0.3</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>micro_precision_pa__0.0</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>micro_precision_pa__0.1</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>micro_precision_pa__0.2</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>micro_precision_pa__0.3</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>micro_recall_pa__0.0</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>micro_recall_pa__0.1</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>micro_recall_pa__0.2</t>
+        </is>
+      </c>
+      <c r="BM1" s="1" t="inlineStr">
+        <is>
+          <t>micro_recall_pa__0.3</t>
+        </is>
+      </c>
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>rec__0.0</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>rec__0.1</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>rec__0.2</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>rec__0.3</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>subset0_1_pa__0.0</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>subset0_1_pa__0.1</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>subset0_1_pa__0.2</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>subset0_1_pa__0.3</t>
         </is>
@@ -623,100 +843,320 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
+          <t>0.7073±0.0585</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0.6712±0.0450</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>0.5855±0.0417</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>0.4241±0.0317</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
           <t>0.9561±0.0018</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>0.9276±0.0021</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>0.8775±0.0036</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>0.7774±0.0046</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>0.6772±0.0100</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>0.5267±0.0102</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>0.3759±0.0120</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>0.2015±0.0055</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>0.6099±0.0080</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0.6254±0.0102</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0.6480±0.0137</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>0.6772±0.0183</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
         <is>
           <t>0.6187±0.0068</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>0.5309±0.0086</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>0.4290±0.0112</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>0.2891±0.0064</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>0.9533±0.0015</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>0.9225±0.0018</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
         <is>
           <t>0.8642±0.0034</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>0.7442±0.0059</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>0.5081±0.0064</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>0.4100±0.0087</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>0.3115±0.0118</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>0.1855±0.0048</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>0.2258±0.0245</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>0.1709±0.0085</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>0.1462±0.0054</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>0.1239±0.0040</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>0.3141±0.0277</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>0.1563±0.0066</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>0.1145±0.0037</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>0.0883±0.0024</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>0.2023±0.0234</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>0.2234±0.0255</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>0.2647±0.0286</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>0.3533±0.0337</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>0.9848±0.0055</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>0.9437±0.0104</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>0.8473±0.0195</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>0.6187±0.0103</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>0.5017±0.0067</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>0.3788±0.0073</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>0.2595±0.0053</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>0.6579±0.0128</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>0.4310±0.0079</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>0.2717±0.0059</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>0.1618±0.0036</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>0.5840±0.0102</t>
+        </is>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>0.6003±0.0095</t>
+        </is>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>0.6253±0.0127</t>
+        </is>
+      </c>
+      <c r="BM2" t="inlineStr">
+        <is>
+          <t>0.6563±0.0146</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
         <is>
           <t>0.1780±0.0148</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="BO2" t="inlineStr">
         <is>
           <t>0.0864±0.0103</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="BP2" t="inlineStr">
         <is>
           <t>0.0282±0.0122</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="BQ2" t="inlineStr">
         <is>
           <t>0.0020±0.0023</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="BR2" t="inlineStr">
         <is>
           <t>0.1717±0.0134</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="BS2" t="inlineStr">
         <is>
           <t>0.0837±0.0098</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="BT2" t="inlineStr">
         <is>
           <t>0.0281±0.0122</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="BU2" t="inlineStr">
         <is>
           <t>0.0020±0.0023</t>
         </is>
@@ -770,100 +1210,320 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
+          <t>0.6976±0.0568</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0.6611±0.0447</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>0.5580±0.0395</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>0.3915±0.0275</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
           <t>0.9557±0.0018</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>0.9239±0.0022</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>0.8663±0.0037</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>0.7572±0.0040</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>0.6678±0.0097</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>0.4991±0.0097</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>0.3402±0.0110</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>0.1861±0.0048</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0.6265±0.0069</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0.6417±0.0097</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0.6679±0.0131</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>0.6947±0.0190</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
         <is>
           <t>0.6235±0.0076</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>0.5220±0.0083</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>0.4092±0.0107</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>0.2746±0.0061</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>0.9529±0.0016</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>0.9186±0.0019</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
         <is>
           <t>0.8521±0.0036</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="AG3" t="inlineStr">
         <is>
           <t>0.7218±0.0053</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>0.5111±0.0083</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>0.3983±0.0089</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>0.2910±0.0109</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>0.1734±0.0045</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>0.2331±0.0263</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>0.1719±0.0076</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>0.1463±0.0048</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>0.1238±0.0039</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>0.3139±0.0246</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>0.1519±0.0062</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>0.1110±0.0034</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>0.0869±0.0023</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>0.2139±0.0272</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>0.2335±0.0256</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>0.2869±0.0272</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>0.3817±0.0309</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>0.9835±0.0054</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>0.9369±0.0102</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>0.8311±0.0239</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>0.6246±0.0111</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>0.4972±0.0068</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>0.3669±0.0067</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>0.2492±0.0048</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>0.6467±0.0131</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>0.4156±0.0076</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>0.2559±0.0055</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>0.1527±0.0030</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>0.6041±0.0113</t>
+        </is>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>0.6190±0.0095</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>0.6477±0.0108</t>
+        </is>
+      </c>
+      <c r="BM3" t="inlineStr">
+        <is>
+          <t>0.6766±0.0158</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
         <is>
           <t>0.1704±0.0144</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="BO3" t="inlineStr">
         <is>
           <t>0.0729±0.0100</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="BP3" t="inlineStr">
         <is>
           <t>0.0210±0.0106</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="BQ3" t="inlineStr">
         <is>
           <t>0.0018±0.0022</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="BR3" t="inlineStr">
         <is>
           <t>0.1645±0.0132</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="BS3" t="inlineStr">
         <is>
           <t>0.0701±0.0100</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="BT3" t="inlineStr">
         <is>
           <t>0.0209±0.0106</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="BU3" t="inlineStr">
         <is>
           <t>0.0018±0.0022</t>
         </is>
@@ -917,100 +1577,320 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
+          <t>0.7072±0.0584</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0.6712±0.0449</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>0.5861±0.0421</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>0.4244±0.0330</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
           <t>0.9561±0.0018</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>0.9275±0.0022</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>0.8773±0.0036</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>0.7767±0.0046</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>0.6774±0.0099</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>0.5265±0.0104</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>0.3746±0.0121</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>0.2003±0.0055</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>0.6090±0.0082</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0.6235±0.0105</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0.6464±0.0134</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>0.6747±0.0182</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
         <is>
           <t>0.6183±0.0068</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>0.5302±0.0087</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>0.4279±0.0111</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>0.2877±0.0065</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>0.9533±0.0015</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>0.9224±0.0019</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
         <is>
           <t>0.8640±0.0034</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="AG4" t="inlineStr">
         <is>
           <t>0.7433±0.0058</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>0.5080±0.0063</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>0.4095±0.0088</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>0.3105±0.0118</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>0.1844±0.0048</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>0.2257±0.0243</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>0.1708±0.0086</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>0.1458±0.0054</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>0.1236±0.0040</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>0.3144±0.0270</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>0.1565±0.0067</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>0.1142±0.0037</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>0.0881±0.0024</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>0.2022±0.0234</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>0.2231±0.0255</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>0.2635±0.0295</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>0.3508±0.0334</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>0.9848±0.0055</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>0.9435±0.0102</t>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>0.8468±0.0201</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>0.6184±0.0102</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>0.5007±0.0067</t>
+        </is>
+      </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>0.3780±0.0074</t>
+        </is>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>0.2583±0.0053</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>0.6582±0.0125</t>
+        </is>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>0.4304±0.0082</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>0.2711±0.0059</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
+          <t>0.1610±0.0036</t>
+        </is>
+      </c>
+      <c r="BJ4" t="inlineStr">
+        <is>
+          <t>0.5831±0.0104</t>
+        </is>
+      </c>
+      <c r="BK4" t="inlineStr">
+        <is>
+          <t>0.5987±0.0093</t>
+        </is>
+      </c>
+      <c r="BL4" t="inlineStr">
+        <is>
+          <t>0.6240±0.0128</t>
+        </is>
+      </c>
+      <c r="BM4" t="inlineStr">
+        <is>
+          <t>0.6543±0.0145</t>
+        </is>
+      </c>
+      <c r="BN4" t="inlineStr">
         <is>
           <t>0.1786±0.0143</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="BO4" t="inlineStr">
         <is>
           <t>0.0866±0.0105</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="BP4" t="inlineStr">
         <is>
           <t>0.0283±0.0121</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="BQ4" t="inlineStr">
         <is>
           <t>0.0020±0.0023</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="BR4" t="inlineStr">
         <is>
           <t>0.1723±0.0129</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="BS4" t="inlineStr">
         <is>
           <t>0.0839±0.0103</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="BT4" t="inlineStr">
         <is>
           <t>0.0282±0.0121</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="BU4" t="inlineStr">
         <is>
           <t>0.0020±0.0023</t>
         </is>
@@ -1064,100 +1944,320 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
+          <t>0.6977±0.0568</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0.6605±0.0452</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>0.5588±0.0393</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>0.3903±0.0279</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
           <t>0.9557±0.0018</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>0.9239±0.0023</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>0.8661±0.0036</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>0.7566±0.0038</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>0.6683±0.0090</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>0.4986±0.0098</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>0.3397±0.0108</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>0.1857±0.0047</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>0.6258±0.0078</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0.6409±0.0105</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>0.6672±0.0125</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0.6934±0.0184</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
         <is>
           <t>0.6233±0.0077</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>0.5214±0.0086</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>0.4087±0.0104</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>0.2739±0.0059</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>0.9529±0.0015</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>0.9185±0.0021</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
         <is>
           <t>0.8517±0.0035</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="AG5" t="inlineStr">
         <is>
           <t>0.7211±0.0054</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>0.5110±0.0080</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>0.3979±0.0090</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>0.2906±0.0107</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>0.1730±0.0044</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>0.2332±0.0270</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>0.1719±0.0076</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>0.1460±0.0045</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>0.1236±0.0039</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>0.3146±0.0256</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>0.1520±0.0064</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>0.1108±0.0032</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>0.0867±0.0022</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>0.2136±0.0277</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>0.2334±0.0255</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>0.2857±0.0271</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>0.3814±0.0321</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>0.9835±0.0054</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>0.9369±0.0112</t>
+        </is>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>0.8307±0.0230</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>0.6241±0.0106</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>0.4967±0.0069</t>
+        </is>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>0.3663±0.0066</t>
+        </is>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>0.2483±0.0044</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>0.6471±0.0121</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>0.4151±0.0081</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>0.2554±0.0055</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
+          <t>0.1521±0.0029</t>
+        </is>
+      </c>
+      <c r="BJ5" t="inlineStr">
+        <is>
+          <t>0.6028±0.0114</t>
+        </is>
+      </c>
+      <c r="BK5" t="inlineStr">
+        <is>
+          <t>0.6184±0.0095</t>
+        </is>
+      </c>
+      <c r="BL5" t="inlineStr">
+        <is>
+          <t>0.6472±0.0107</t>
+        </is>
+      </c>
+      <c r="BM5" t="inlineStr">
+        <is>
+          <t>0.6754±0.0153</t>
+        </is>
+      </c>
+      <c r="BN5" t="inlineStr">
         <is>
           <t>0.1710±0.0140</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="BO5" t="inlineStr">
         <is>
           <t>0.0729±0.0101</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="BP5" t="inlineStr">
         <is>
           <t>0.0216±0.0108</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="BQ5" t="inlineStr">
         <is>
           <t>0.0019±0.0022</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="BR5" t="inlineStr">
         <is>
           <t>0.1646±0.0124</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="BS5" t="inlineStr">
         <is>
           <t>0.0702±0.0101</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="BT5" t="inlineStr">
         <is>
           <t>0.0215±0.0108</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
+      <c r="BU5" t="inlineStr">
         <is>
           <t>0.0019±0.0022</t>
         </is>
@@ -1211,100 +2311,320 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
+          <t>0.7203±0.0536</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0.6859±0.0425</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>0.6280±0.0371</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>0.5091±0.0392</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
           <t>0.9552±0.0016</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>0.9292±0.0022</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>0.8833±0.0034</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>0.7971±0.0047</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>0.6868±0.0104</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>0.5515±0.0109</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>0.4113±0.0127</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>0.2321±0.0081</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>0.5792±0.0060</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0.5927±0.0123</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>0.5987±0.0125</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>0.6269±0.0146</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
         <is>
           <t>0.6023±0.0043</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>0.5283±0.0100</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>0.4341±0.0099</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>0.3088±0.0068</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>0.9527±0.0013</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>0.9262±0.0021</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
         <is>
           <t>0.8808±0.0032</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="AG6" t="inlineStr">
         <is>
           <t>0.7958±0.0049</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>0.4891±0.0042</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>0.4070±0.0104</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>0.3153±0.0095</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>0.2013±0.0055</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>0.2155±0.0278</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>0.1686±0.0089</t>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>0.1435±0.0054</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>0.1247±0.0040</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>0.3135±0.0404</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>0.1620±0.0072</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>0.1184±0.0038</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>0.0918±0.0025</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>0.1892±0.0248</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>0.2100±0.0244</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>0.2377±0.0267</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>0.2990±0.0335</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>0.9871±0.0048</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>0.9535±0.0089</t>
+        </is>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>0.8865±0.0135</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>0.6060±0.0099</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>0.5009±0.0073</t>
+        </is>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>0.3844±0.0078</t>
+        </is>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>0.2755±0.0054</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>0.6697±0.0130</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>0.4487±0.0087</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>0.2883±0.0071</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>0.1783±0.0040</t>
+        </is>
+      </c>
+      <c r="BJ6" t="inlineStr">
+        <is>
+          <t>0.5535±0.0094</t>
+        </is>
+      </c>
+      <c r="BK6" t="inlineStr">
+        <is>
+          <t>0.5671±0.0088</t>
+        </is>
+      </c>
+      <c r="BL6" t="inlineStr">
+        <is>
+          <t>0.5766±0.0090</t>
+        </is>
+      </c>
+      <c r="BM6" t="inlineStr">
+        <is>
+          <t>0.6061±0.0127</t>
+        </is>
+      </c>
+      <c r="BN6" t="inlineStr">
         <is>
           <t>0.1569±0.0124</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="BO6" t="inlineStr">
         <is>
           <t>0.0829±0.0138</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="BP6" t="inlineStr">
         <is>
           <t>0.0263±0.0074</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="BQ6" t="inlineStr">
         <is>
           <t>0.0011±0.0014</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="BR6" t="inlineStr">
         <is>
           <t>0.1509±0.0104</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="BS6" t="inlineStr">
         <is>
           <t>0.0803±0.0130</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="BT6" t="inlineStr">
         <is>
           <t>0.0263±0.0074</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="BU6" t="inlineStr">
         <is>
           <t>0.0011±0.0014</t>
         </is>
@@ -1358,100 +2678,320 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
+          <t>0.7026±0.0496</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0.6623±0.0408</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>0.5578±0.0382</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>0.3710±0.0241</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
           <t>0.9539±0.0017</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>0.9210±0.0022</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>0.8528±0.0044</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>0.7006±0.0052</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>0.6626±0.0140</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>0.4908±0.0104</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>0.3131±0.0108</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>0.1480±0.0034</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>0.6128±0.0099</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>0.6319±0.0114</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>0.6613±0.0124</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>0.7087±0.0164</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
         <is>
           <t>0.6119±0.0081</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>0.5129±0.0078</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>0.3871±0.0100</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>0.2343±0.0048</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>0.9512±0.0016</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>0.9177±0.0019</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="AF7" t="inlineStr">
         <is>
           <t>0.8496±0.0042</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="AG7" t="inlineStr">
         <is>
           <t>0.6984±0.0053</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>0.4975±0.0081</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>0.3868±0.0091</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>0.2671±0.0094</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>0.1392±0.0033</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>0.2258±0.0206</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>0.1708±0.0068</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>0.1453±0.0053</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>0.1214±0.0034</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>0.2999±0.0262</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>0.1513±0.0056</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>0.1092±0.0038</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>0.0837±0.0022</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>0.2106±0.0255</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>0.2320±0.0248</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>0.2933±0.0284</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>0.4028±0.0307</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>0.9826±0.0054</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>0.9342±0.0113</t>
+        </is>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>0.8026±0.0164</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>0.6151±0.0106</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>0.4919±0.0065</t>
+        </is>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>0.3555±0.0081</t>
+        </is>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>0.2274±0.0045</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>0.6398±0.0187</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>0.4120±0.0075</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>0.2458±0.0069</t>
+        </is>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
+          <t>0.1360±0.0030</t>
+        </is>
+      </c>
+      <c r="BJ7" t="inlineStr">
+        <is>
+          <t>0.5925±0.0064</t>
+        </is>
+      </c>
+      <c r="BK7" t="inlineStr">
+        <is>
+          <t>0.6106±0.0083</t>
+        </is>
+      </c>
+      <c r="BL7" t="inlineStr">
+        <is>
+          <t>0.6424±0.0101</t>
+        </is>
+      </c>
+      <c r="BM7" t="inlineStr">
+        <is>
+          <t>0.6925±0.0140</t>
+        </is>
+      </c>
+      <c r="BN7" t="inlineStr">
         <is>
           <t>0.1551±0.0068</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="BO7" t="inlineStr">
         <is>
           <t>0.0594±0.0132</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="BP7" t="inlineStr">
         <is>
           <t>0.0101±0.0073</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="BQ7" t="inlineStr">
         <is>
           <t>0.0000±0.0000</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="BR7" t="inlineStr">
         <is>
           <t>0.1496±0.0063</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="BS7" t="inlineStr">
         <is>
           <t>0.0567±0.0127</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="BT7" t="inlineStr">
         <is>
           <t>0.0101±0.0073</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="BU7" t="inlineStr">
         <is>
           <t>0.0000±0.0000</t>
         </is>
@@ -1505,100 +3045,320 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
+          <t>0.7318±0.0560</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0.6914±0.0429</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>0.6349±0.0368</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>0.5176±0.0380</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
           <t>0.9550±0.0015</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>0.9302±0.0022</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>0.8850±0.0033</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>0.8006±0.0048</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>0.6902±0.0088</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>0.5614±0.0112</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>0.4194±0.0130</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>0.2370±0.0086</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>0.5683±0.0075</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0.5824±0.0118</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>0.5872±0.0124</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>0.6146±0.0150</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
         <is>
           <t>0.5964±0.0052</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>0.5282±0.0100</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>0.4351±0.0096</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>0.3108±0.0072</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>0.9524±0.0013</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>0.9273±0.0021</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="AF8" t="inlineStr">
         <is>
           <t>0.8825±0.0031</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="AG8" t="inlineStr">
         <is>
           <t>0.7992±0.0049</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>0.4829±0.0046</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>0.4081±0.0100</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>0.3169±0.0092</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>0.2035±0.0060</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>0.2017±0.0265</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>0.1664±0.0088</t>
+        </is>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>0.1418±0.0054</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>0.1235±0.0042</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>0.2980±0.0452</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>0.1628±0.0069</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>0.1184±0.0039</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>0.0917±0.0026</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>0.1757±0.0216</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>0.2036±0.0238</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>0.2306±0.0270</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>0.2904±0.0321</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>0.9878±0.0049</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>0.9539±0.0079</t>
+        </is>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>0.8879±0.0129</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>0.5990±0.0097</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>0.4995±0.0077</t>
+        </is>
+      </c>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>0.3830±0.0076</t>
+        </is>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>0.2751±0.0055</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>0.6724±0.0114</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>0.4536±0.0092</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>0.2897±0.0072</t>
+        </is>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
+          <t>0.1790±0.0041</t>
+        </is>
+      </c>
+      <c r="BJ8" t="inlineStr">
+        <is>
+          <t>0.5401±0.0099</t>
+        </is>
+      </c>
+      <c r="BK8" t="inlineStr">
+        <is>
+          <t>0.5558±0.0096</t>
+        </is>
+      </c>
+      <c r="BL8" t="inlineStr">
+        <is>
+          <t>0.5648±0.0093</t>
+        </is>
+      </c>
+      <c r="BM8" t="inlineStr">
+        <is>
+          <t>0.5947±0.0127</t>
+        </is>
+      </c>
+      <c r="BN8" t="inlineStr">
         <is>
           <t>0.1522±0.0122</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="BO8" t="inlineStr">
         <is>
           <t>0.0868±0.0116</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="BP8" t="inlineStr">
         <is>
           <t>0.0289±0.0078</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="BQ8" t="inlineStr">
         <is>
           <t>0.0013±0.0017</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="BR8" t="inlineStr">
         <is>
           <t>0.1462±0.0100</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="BS8" t="inlineStr">
         <is>
           <t>0.0843±0.0115</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="BT8" t="inlineStr">
         <is>
           <t>0.0289±0.0078</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="BU8" t="inlineStr">
         <is>
           <t>0.0013±0.0017</t>
         </is>
@@ -1652,100 +3412,320 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
+          <t>0.7028±0.0499</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0.6620±0.0412</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>0.5600±0.0371</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>0.3774±0.0271</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
           <t>0.9545±0.0015</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>0.9209±0.0023</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>0.8534±0.0042</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>0.7058±0.0056</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>0.6656±0.0132</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>0.4905±0.0109</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>0.3130±0.0104</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>0.1484±0.0037</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>0.6142±0.0079</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>0.6310±0.0114</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>0.6595±0.0123</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>0.7033±0.0168</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
         <is>
           <t>0.6145±0.0068</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>0.5124±0.0083</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>0.3867±0.0096</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>0.2347±0.0053</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>0.9518±0.0013</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="AE9" t="inlineStr">
         <is>
           <t>0.9176±0.0021</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="AF9" t="inlineStr">
         <is>
           <t>0.8500±0.0039</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="AG9" t="inlineStr">
         <is>
           <t>0.7035±0.0057</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>0.5004±0.0070</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>0.3866±0.0096</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>0.2667±0.0089</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>0.1395±0.0035</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>0.2310±0.0242</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>0.1710±0.0069</t>
+        </is>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>0.1449±0.0051</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>0.1216±0.0034</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>0.3131±0.0242</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>0.1514±0.0057</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>0.1091±0.0037</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>0.0840±0.0023</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>0.2107±0.0254</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>0.2322±0.0248</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>0.2912±0.0272</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>0.3952±0.0306</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>0.9823±0.0054</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>0.9357±0.0113</t>
+        </is>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>0.8111±0.0178</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>0.6182±0.0092</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>0.4915±0.0068</t>
+        </is>
+      </c>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>0.3557±0.0077</t>
+        </is>
+      </c>
+      <c r="BE9" t="inlineStr">
+        <is>
+          <t>0.2291±0.0050</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>0.6459±0.0150</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>0.4117±0.0080</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>0.2462±0.0065</t>
+        </is>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
+          <t>0.1375±0.0033</t>
+        </is>
+      </c>
+      <c r="BJ9" t="inlineStr">
+        <is>
+          <t>0.5928±0.0065</t>
+        </is>
+      </c>
+      <c r="BK9" t="inlineStr">
+        <is>
+          <t>0.6099±0.0085</t>
+        </is>
+      </c>
+      <c r="BL9" t="inlineStr">
+        <is>
+          <t>0.6407±0.0096</t>
+        </is>
+      </c>
+      <c r="BM9" t="inlineStr">
+        <is>
+          <t>0.6870±0.0137</t>
+        </is>
+      </c>
+      <c r="BN9" t="inlineStr">
         <is>
           <t>0.1580±0.0094</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="BO9" t="inlineStr">
         <is>
           <t>0.0598±0.0136</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="BP9" t="inlineStr">
         <is>
           <t>0.0101±0.0070</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
+      <c r="BQ9" t="inlineStr">
         <is>
           <t>0.0000±0.0000</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="BR9" t="inlineStr">
         <is>
           <t>0.1521±0.0089</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="BS9" t="inlineStr">
         <is>
           <t>0.0572±0.0132</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="BT9" t="inlineStr">
         <is>
           <t>0.0101±0.0070</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="BU9" t="inlineStr">
         <is>
           <t>0.0000±0.0000</t>
         </is>
